--- a/data/trans_orig/P15C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15C-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25399</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48247</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>71006</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>51596</t>
+          <t>51136</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>70832</t>
+          <t>69584</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>104205</t>
+          <t>104432</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>133492</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>33184</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>58240</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27252</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42120</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>36392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74375</t>
+          <t>74158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>65689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90648</t>
+          <t>91484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115449</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -6530,12 +6530,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71074</t>
+          <t>70991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71048</t>
+          <t>70080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>29613</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>88967</t>
+          <t>88527</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>113615</t>
+          <t>113092</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24082</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26629</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>30900</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>49419</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>171586</t>
+          <t>171603</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>203516</t>
+          <t>205642</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>123343</t>
+          <t>125507</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>157410</t>
+          <t>157415</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>305880</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>348981</t>
+          <t>352729</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>29463</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>95133</t>
+          <t>95815</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>30700</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>46679</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76373</t>
+          <t>75944</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46187</t>
+          <t>45644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63628</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -9942,12 +9942,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44373</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>41912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63209</t>
+          <t>63273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83145</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28219</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10737,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10822,12 +10822,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10935,12 +10935,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>22501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11048,12 +11048,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22632</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11567,12 +11567,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11582,12 +11582,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11602,12 +11602,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -11645,12 +11645,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -11758,12 +11758,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44255</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>27050</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>84493</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25673</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>846</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12342,12 +12342,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12362,12 +12362,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>24883</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>101756</t>
+          <t>101631</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>129729</t>
+          <t>129813</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>105724</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>134161</t>
+          <t>132937</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>218811</t>
+          <t>216542</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>258074</t>
+          <t>256589</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>49092</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>87006</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -13349,32 +13349,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13384,32 +13384,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13419,32 +13419,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -13462,32 +13462,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13497,32 +13497,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13532,32 +13532,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -13575,32 +13575,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>39380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13610,32 +13610,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28754</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13645,32 +13645,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>57077</t>
+          <t>63548</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -13688,32 +13688,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13723,32 +13723,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13758,32 +13758,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>27646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -14027,17 +14027,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14062,17 +14062,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14097,17 +14097,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14144,32 +14144,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14179,32 +14179,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14214,32 +14214,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -14257,32 +14257,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14292,32 +14292,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14327,32 +14327,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>27402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -14370,32 +14370,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>42636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14405,32 +14405,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14440,32 +14440,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>70446</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>83481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -14483,32 +14483,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14518,32 +14518,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14553,32 +14553,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>22893</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -14606,12 +14606,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -14641,12 +14641,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14666,32 +14666,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -14822,17 +14822,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14857,17 +14857,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14892,17 +14892,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>137618</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>137618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>137618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14939,32 +14939,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14974,32 +14974,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15009,32 +15009,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -15052,32 +15052,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15087,32 +15087,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15122,32 +15122,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -15165,32 +15165,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15200,32 +15200,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15235,32 +15235,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47219</t>
+          <t>52750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -15278,32 +15278,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15313,32 +15313,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15348,32 +15348,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -15471,12 +15471,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15504,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -15549,12 +15549,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -15584,12 +15584,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -15617,17 +15617,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15652,17 +15652,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15687,17 +15687,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15734,32 +15734,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15769,32 +15769,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15804,32 +15804,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15857,12 +15857,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15882,32 +15882,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15917,32 +15917,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -15960,32 +15960,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>39187</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>46499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15995,32 +15995,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42683</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35900</t>
+          <t>37003</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16030,32 +16030,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>76861</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>67106</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87222</t>
+          <t>93110</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -16073,32 +16073,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16108,32 +16108,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16143,32 +16143,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>34374</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>44804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16221,32 +16221,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16256,32 +16256,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -16412,17 +16412,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16482,17 +16482,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16529,32 +16529,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16564,32 +16564,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16599,32 +16599,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -16642,32 +16642,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16677,32 +16677,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>23026</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -16712,32 +16712,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -16755,32 +16755,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>116189</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>83317</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113184</t>
+          <t>133541</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>135572</t>
+          <t>145620</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>124737</t>
+          <t>131868</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>146626</t>
+          <t>157197</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16825,32 +16825,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>234415</t>
+          <t>261809</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>213571</t>
+          <t>241127</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>256550</t>
+          <t>284069</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -16868,102 +16868,102 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>48241</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36625</t>
+          <t>38061</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>62105</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>17,22%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>47933</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>38402</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>58542</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>20,64%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>97954</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>82985</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>115620</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>18,31%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>42324</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>33986</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>51511</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>90565</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>75219</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>106477</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -16981,32 +16981,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17016,32 +17016,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17051,32 +17051,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17104,12 +17104,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -17139,12 +17139,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -17207,17 +17207,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17242,17 +17242,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17277,17 +17277,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
